--- a/data/trans_orig/BARTHEL_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/BARTHEL_R2-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel) en 2007</t>
+          <t>Población con dependencia funcional para actividades básicas de la vida diaria de grado moderado o superior (Barthel) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6649</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19320</t>
+          <t>19621</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9649</t>
+          <t>9204</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24849</t>
+          <t>25677</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18712</t>
+          <t>19669</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39280</t>
+          <t>40265</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,22%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>95669</t>
+          <t>95368</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>108340</t>
+          <t>108219</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>124686</t>
+          <t>123858</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>139886</t>
+          <t>140331</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>225244</t>
+          <t>224259</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>245812</t>
+          <t>244855</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,56%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6593</t>
+          <t>6458</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19946</t>
+          <t>20416</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17992</t>
+          <t>18331</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38310</t>
+          <t>39698</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27767</t>
+          <t>27724</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50320</t>
+          <t>52550</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>125943</t>
+          <t>125473</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>139296</t>
+          <t>139431</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>144370</t>
+          <t>142982</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>164688</t>
+          <t>164349</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>278248</t>
+          <t>276018</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>300801</t>
+          <t>300844</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,56%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>968</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8837</t>
+          <t>8479</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9156</t>
+          <t>9294</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24558</t>
+          <t>24062</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12289</t>
+          <t>12730</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29132</t>
+          <t>29720</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,37%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>95534</t>
+          <t>95892</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>103443</t>
+          <t>103403</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>111292</t>
+          <t>111788</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>126694</t>
+          <t>126556</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>211089</t>
+          <t>210501</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>227932</t>
+          <t>227491</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,7%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>7223</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19406</t>
+          <t>19911</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22524</t>
+          <t>23115</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43506</t>
+          <t>43255</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32187</t>
+          <t>33451</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59419</t>
+          <t>57891</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>117811</t>
+          <t>117306</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>130707</t>
+          <t>129994</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>165271</t>
+          <t>165522</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>186253</t>
+          <t>185662</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>286576</t>
+          <t>288104</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>313808</t>
+          <t>312544</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,33%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29898</t>
+          <t>29182</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53228</t>
+          <t>52301</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>74229</t>
+          <t>73382</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>111261</t>
+          <t>109071</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>112046</t>
+          <t>109799</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>155501</t>
+          <t>153994</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,06%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>449238</t>
+          <t>450165</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>472568</t>
+          <t>473284</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>565581</t>
+          <t>567771</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>602613</t>
+          <t>603460</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1023807</t>
+          <t>1025314</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1067262</t>
+          <t>1069509</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,69%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel) en 2012</t>
+          <t>Población con dependencia funcional para actividades básicas de la vida diaria de grado moderado o superior (Barthel) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6529</t>
+          <t>6380</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19931</t>
+          <t>20355</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30599</t>
+          <t>30851</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53284</t>
+          <t>52946</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39923</t>
+          <t>42007</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67711</t>
+          <t>69160</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>119616</t>
+          <t>119192</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>133018</t>
+          <t>133167</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>113503</t>
+          <t>113841</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>136188</t>
+          <t>135936</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>238623</t>
+          <t>237174</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>266411</t>
+          <t>264327</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>86,29%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21859</t>
+          <t>22869</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44120</t>
+          <t>44447</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49633</t>
+          <t>49129</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75295</t>
+          <t>76370</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>78518</t>
+          <t>79016</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>113768</t>
+          <t>112559</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,5%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>110758</t>
+          <t>110431</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>133019</t>
+          <t>132009</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>116125</t>
+          <t>115050</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>141787</t>
+          <t>142291</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>232530</t>
+          <t>233739</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>267780</t>
+          <t>267282</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,18%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7674</t>
+          <t>7506</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26667</t>
+          <t>24471</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30636</t>
+          <t>29807</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53400</t>
+          <t>52248</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42343</t>
+          <t>42025</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71344</t>
+          <t>70381</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>28,77%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76931</t>
+          <t>79127</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>95924</t>
+          <t>96092</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>87619</t>
+          <t>88771</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>110383</t>
+          <t>111212</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>173273</t>
+          <t>174236</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>202274</t>
+          <t>202592</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,82%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15145</t>
+          <t>15526</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34686</t>
+          <t>35056</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36712</t>
+          <t>35553</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61693</t>
+          <t>61982</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56774</t>
+          <t>56811</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>90026</t>
+          <t>90109</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,23%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>126927</t>
+          <t>126557</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>146468</t>
+          <t>146087</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>182057</t>
+          <t>181768</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>207038</t>
+          <t>208197</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>315337</t>
+          <t>315254</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>348589</t>
+          <t>348552</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>65298</t>
+          <t>65275</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>103386</t>
+          <t>101241</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>167530</t>
+          <t>171211</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>217976</t>
+          <t>219312</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>246375</t>
+          <t>246971</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>305797</t>
+          <t>309586</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,77%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>456251</t>
+          <t>458396</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>494339</t>
+          <t>494362</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>524999</t>
+          <t>523663</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>575445</t>
+          <t>571764</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>996815</t>
+          <t>993026</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1056237</t>
+          <t>1055641</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,04%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel) en 2016</t>
+          <t>Población con dependencia funcional para actividades básicas de la vida diaria de grado moderado o superior (Barthel) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12750</t>
+          <t>13146</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28842</t>
+          <t>28543</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30327</t>
+          <t>29706</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54968</t>
+          <t>55182</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46913</t>
+          <t>47750</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75956</t>
+          <t>75517</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,35%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>107892</t>
+          <t>108191</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>123984</t>
+          <t>123588</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>118423</t>
+          <t>118209</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>143064</t>
+          <t>143685</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>234169</t>
+          <t>234608</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>263212</t>
+          <t>262375</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,6%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13582</t>
+          <t>14006</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30454</t>
+          <t>30362</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28979</t>
+          <t>29575</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54751</t>
+          <t>56021</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46099</t>
+          <t>47767</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>77670</t>
+          <t>79355</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,66%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>134487</t>
+          <t>134579</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>151359</t>
+          <t>150935</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>164412</t>
+          <t>163142</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>190184</t>
+          <t>189588</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>306434</t>
+          <t>304749</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>338005</t>
+          <t>336337</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,56%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7194</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20603</t>
+          <t>20096</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26084</t>
+          <t>26687</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48588</t>
+          <t>49167</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35895</t>
+          <t>37390</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63309</t>
+          <t>64590</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>25,07%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94432</t>
+          <t>94939</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>107841</t>
+          <t>108626</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>94008</t>
+          <t>93429</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>116512</t>
+          <t>115909</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>194322</t>
+          <t>193041</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>221736</t>
+          <t>220241</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>85,49%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9848</t>
+          <t>9820</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24982</t>
+          <t>25946</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37690</t>
+          <t>38006</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66329</t>
+          <t>66616</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52014</t>
+          <t>52006</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84866</t>
+          <t>84451</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,23%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>149636</t>
+          <t>148672</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>164770</t>
+          <t>164798</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>176452</t>
+          <t>176165</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>205091</t>
+          <t>204775</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>332534</t>
+          <t>332949</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>365386</t>
+          <t>365394</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>56089</t>
+          <t>56165</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>85115</t>
+          <t>86052</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>144700</t>
+          <t>145837</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>195885</t>
+          <t>198271</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>212065</t>
+          <t>210422</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>273597</t>
+          <t>267800</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,56%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>506213</t>
+          <t>505276</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>535239</t>
+          <t>535163</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>582046</t>
+          <t>579660</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>633231</t>
+          <t>632094</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1095662</t>
+          <t>1101459</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1157194</t>
+          <t>1158837</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,63%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel) en 2023</t>
+          <t>Población con dependencia funcional para actividades básicas de la vida diaria de grado moderado o superior (Barthel) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14216</t>
+          <t>13970</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26802</t>
+          <t>27506</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38242</t>
+          <t>38247</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53459</t>
+          <t>52621</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>56044</t>
+          <t>56064</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75402</t>
+          <t>76396</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,53%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>120027</t>
+          <t>119323</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>132613</t>
+          <t>132859</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>124387</t>
+          <t>125225</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>139604</t>
+          <t>139599</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>249273</t>
+          <t>248279</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>268631</t>
+          <t>268611</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,73%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18076</t>
+          <t>18391</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32405</t>
+          <t>33275</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43313</t>
+          <t>43507</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61087</t>
+          <t>61291</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>66391</t>
+          <t>66593</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>88661</t>
+          <t>89033</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,61%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>127709</t>
+          <t>126839</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>142038</t>
+          <t>141723</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>155860</t>
+          <t>155656</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>173634</t>
+          <t>173440</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>288400</t>
+          <t>288028</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>310670</t>
+          <t>310468</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,34%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9877</t>
+          <t>9426</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22796</t>
+          <t>22465</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8858</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>78789</t>
+          <t>80951</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16299</t>
+          <t>14848</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>86860</t>
+          <t>85488</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,21%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>114156</t>
+          <t>114487</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>127075</t>
+          <t>127526</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>280874</t>
+          <t>278712</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>350805</t>
+          <t>351464</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>409755</t>
+          <t>411127</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>480316</t>
+          <t>481767</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17742</t>
+          <t>17632</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32439</t>
+          <t>32398</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48980</t>
+          <t>50013</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68994</t>
+          <t>68940</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>69356</t>
+          <t>70728</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>95619</t>
+          <t>95604</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>171985</t>
+          <t>172026</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>186682</t>
+          <t>186792</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>204359</t>
+          <t>204413</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>224373</t>
+          <t>223340</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>382159</t>
+          <t>382174</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>408422</t>
+          <t>407050</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,2%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>71941</t>
+          <t>71839</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>98875</t>
+          <t>99136</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>108560</t>
+          <t>100373</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>243644</t>
+          <t>241687</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>192746</t>
+          <t>172260</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>319041</t>
+          <t>320343</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,11%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>549445</t>
+          <t>549184</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>576379</t>
+          <t>576481</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>784166</t>
+          <t>786123</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>919250</t>
+          <t>927437</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1357089</t>
+          <t>1355787</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1483384</t>
+          <t>1503870</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>89,72%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/BARTHEL_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/BARTHEL_R2-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19621</t>
+          <t>19701</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9204</t>
+          <t>9303</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25677</t>
+          <t>25902</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19669</t>
+          <t>19876</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40265</t>
+          <t>40580</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,34%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>95368</t>
+          <t>95288</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>108219</t>
+          <t>107712</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>123858</t>
+          <t>123633</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>140331</t>
+          <t>140232</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>224259</t>
+          <t>223944</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>244855</t>
+          <t>244648</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,49%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6458</t>
+          <t>5945</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20416</t>
+          <t>18017</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18331</t>
+          <t>17612</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39698</t>
+          <t>39083</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27724</t>
+          <t>28350</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52550</t>
+          <t>53092</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,16%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>125473</t>
+          <t>127872</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>139431</t>
+          <t>139944</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>142982</t>
+          <t>143597</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>164349</t>
+          <t>165068</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>276018</t>
+          <t>275476</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>300844</t>
+          <t>300218</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,37%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>921</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8479</t>
+          <t>8733</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9294</t>
+          <t>9103</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24062</t>
+          <t>25273</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12730</t>
+          <t>12226</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29720</t>
+          <t>29386</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,23%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>95892</t>
+          <t>95638</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>103403</t>
+          <t>103450</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>111788</t>
+          <t>110577</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>126556</t>
+          <t>126747</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>210501</t>
+          <t>210835</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>227491</t>
+          <t>227995</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,91%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7223</t>
+          <t>6664</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19911</t>
+          <t>19303</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23115</t>
+          <t>22031</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43255</t>
+          <t>43066</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33451</t>
+          <t>32689</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>57891</t>
+          <t>57720</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,68%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>117306</t>
+          <t>117914</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>129994</t>
+          <t>130553</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>165522</t>
+          <t>165711</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>185662</t>
+          <t>186746</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>288104</t>
+          <t>288275</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>312544</t>
+          <t>313306</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,55%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29182</t>
+          <t>31162</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>52301</t>
+          <t>53936</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>73382</t>
+          <t>75498</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>109071</t>
+          <t>111199</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>109799</t>
+          <t>110431</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>153994</t>
+          <t>153159</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>450165</t>
+          <t>448530</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>473284</t>
+          <t>471304</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>567771</t>
+          <t>565643</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>603460</t>
+          <t>601344</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1025314</t>
+          <t>1026149</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1069509</t>
+          <t>1068877</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,64%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6380</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20355</t>
+          <t>20286</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30851</t>
+          <t>31277</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52946</t>
+          <t>52633</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42007</t>
+          <t>41661</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69160</t>
+          <t>70406</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,98%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>119192</t>
+          <t>119261</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>133167</t>
+          <t>132657</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>113841</t>
+          <t>114154</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>135936</t>
+          <t>135510</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>237174</t>
+          <t>235928</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>264327</t>
+          <t>264673</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,4%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22869</t>
+          <t>22106</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44447</t>
+          <t>44752</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49129</t>
+          <t>49577</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>76370</t>
+          <t>75356</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>79016</t>
+          <t>78716</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>112559</t>
+          <t>111532</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,21%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>110431</t>
+          <t>110126</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>132009</t>
+          <t>132772</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>115050</t>
+          <t>116064</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>142291</t>
+          <t>141843</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>233739</t>
+          <t>234766</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>267282</t>
+          <t>267582</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,27%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7506</t>
+          <t>7806</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24471</t>
+          <t>25355</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29807</t>
+          <t>28947</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52248</t>
+          <t>50847</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42025</t>
+          <t>42921</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70381</t>
+          <t>69953</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,6%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79127</t>
+          <t>78243</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>96092</t>
+          <t>95792</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>88771</t>
+          <t>90172</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>111212</t>
+          <t>112072</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>174236</t>
+          <t>174664</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>202592</t>
+          <t>201696</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>82,45%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15526</t>
+          <t>14815</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35056</t>
+          <t>35263</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35553</t>
+          <t>37424</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61982</t>
+          <t>62128</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56811</t>
+          <t>57536</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>90109</t>
+          <t>89216</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,01%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>126557</t>
+          <t>126350</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>146087</t>
+          <t>146798</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>181768</t>
+          <t>181622</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>208197</t>
+          <t>206326</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>315254</t>
+          <t>316147</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>348552</t>
+          <t>347827</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>85,81%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>65275</t>
+          <t>67035</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>101241</t>
+          <t>102984</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>171211</t>
+          <t>166780</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>219312</t>
+          <t>215353</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>246971</t>
+          <t>247130</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>309586</t>
+          <t>306910</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,56%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>458396</t>
+          <t>456653</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>494362</t>
+          <t>492602</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>523663</t>
+          <t>527622</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>571764</t>
+          <t>576195</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>993026</t>
+          <t>995702</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1055641</t>
+          <t>1055482</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,03%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13146</t>
+          <t>13005</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28543</t>
+          <t>29047</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29706</t>
+          <t>29164</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55182</t>
+          <t>52019</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47750</t>
+          <t>47042</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75517</t>
+          <t>75808</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,44%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>108191</t>
+          <t>107687</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>123588</t>
+          <t>123729</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>118209</t>
+          <t>121372</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>143685</t>
+          <t>144227</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>234608</t>
+          <t>234317</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>262375</t>
+          <t>263083</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,83%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14006</t>
+          <t>13827</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30362</t>
+          <t>29376</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29575</t>
+          <t>28945</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56021</t>
+          <t>54124</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47767</t>
+          <t>47441</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>79355</t>
+          <t>76335</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>134579</t>
+          <t>135565</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>150935</t>
+          <t>151114</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>163142</t>
+          <t>165039</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>189588</t>
+          <t>190218</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>304749</t>
+          <t>307769</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>336337</t>
+          <t>336663</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,65%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20096</t>
+          <t>20895</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26687</t>
+          <t>25382</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49167</t>
+          <t>47984</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37390</t>
+          <t>37172</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64590</t>
+          <t>64320</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,97%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94939</t>
+          <t>94140</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>108626</t>
+          <t>107922</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>93429</t>
+          <t>94612</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>115909</t>
+          <t>117214</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>193041</t>
+          <t>193311</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>220241</t>
+          <t>220459</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,57%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9820</t>
+          <t>10607</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25946</t>
+          <t>25895</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38006</t>
+          <t>37053</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66616</t>
+          <t>65624</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52006</t>
+          <t>52191</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84451</t>
+          <t>84620</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,27%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>148672</t>
+          <t>148723</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>164798</t>
+          <t>164011</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>176165</t>
+          <t>177157</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>204775</t>
+          <t>205728</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>332949</t>
+          <t>332780</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>365394</t>
+          <t>365209</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,5%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>56165</t>
+          <t>56185</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>86052</t>
+          <t>86038</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>145837</t>
+          <t>145972</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>198271</t>
+          <t>195591</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>210422</t>
+          <t>211551</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>267800</t>
+          <t>270154</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,73%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>505276</t>
+          <t>505290</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>535163</t>
+          <t>535143</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>579660</t>
+          <t>582340</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>632094</t>
+          <t>631959</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1101459</t>
+          <t>1099105</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1158837</t>
+          <t>1157708</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,55%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>20016</t>
+          <t>20468</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13970</t>
+          <t>14720</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27506</t>
+          <t>27834</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>45313</t>
+          <t>48188</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38247</t>
+          <t>41122</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52621</t>
+          <t>56436</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>65329</t>
+          <t>68656</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>56064</t>
+          <t>58209</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>76396</t>
+          <t>80743</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>22,98%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>126813</t>
+          <t>141340</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>119323</t>
+          <t>133974</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>132859</t>
+          <t>147088</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>132533</t>
+          <t>141353</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>125225</t>
+          <t>133105</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>139599</t>
+          <t>148419</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>259346</t>
+          <t>282694</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>248279</t>
+          <t>270607</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>268611</t>
+          <t>293141</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>83,43%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>146829</t>
+          <t>161808</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>146829</t>
+          <t>161808</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>146829</t>
+          <t>161808</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>177846</t>
+          <t>189541</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>177846</t>
+          <t>189541</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>177846</t>
+          <t>189541</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>324675</t>
+          <t>351350</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>324675</t>
+          <t>351350</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>324675</t>
+          <t>351350</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25072</t>
+          <t>27196</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18391</t>
+          <t>20245</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33275</t>
+          <t>36873</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>51733</t>
+          <t>56654</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43507</t>
+          <t>46872</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61291</t>
+          <t>66428</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>76805</t>
+          <t>83850</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>66593</t>
+          <t>72436</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>89033</t>
+          <t>97152</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,21%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>135042</t>
+          <t>151008</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>126839</t>
+          <t>141331</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>141723</t>
+          <t>157959</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>165214</t>
+          <t>183692</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>155656</t>
+          <t>173918</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>173440</t>
+          <t>193474</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>300256</t>
+          <t>334700</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>288028</t>
+          <t>321398</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>310468</t>
+          <t>346114</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,69%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>216947</t>
+          <t>240346</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>216947</t>
+          <t>240346</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>216947</t>
+          <t>240346</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>377061</t>
+          <t>418550</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>377061</t>
+          <t>418550</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>377061</t>
+          <t>418550</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15662</t>
+          <t>17435</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9426</t>
+          <t>10814</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22465</t>
+          <t>25608</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>32218</t>
+          <t>36325</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>28629</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80951</t>
+          <t>46112</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>47880</t>
+          <t>53760</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14848</t>
+          <t>43411</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>85488</t>
+          <t>66413</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>19,88%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>121290</t>
+          <t>142350</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>114487</t>
+          <t>134177</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>127526</t>
+          <t>148971</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>327445</t>
+          <t>137976</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>278712</t>
+          <t>128189</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>351464</t>
+          <t>145672</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>448735</t>
+          <t>280325</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>411127</t>
+          <t>267672</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>481767</t>
+          <t>290674</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>87,01%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>359663</t>
+          <t>174301</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>359663</t>
+          <t>174301</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>359663</t>
+          <t>174301</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>496615</t>
+          <t>334085</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>496615</t>
+          <t>334085</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>496615</t>
+          <t>334085</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>24361</t>
+          <t>25265</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17632</t>
+          <t>18693</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32398</t>
+          <t>33249</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>58785</t>
+          <t>65416</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50013</t>
+          <t>55467</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68940</t>
+          <t>77365</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>83146</t>
+          <t>90681</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>70728</t>
+          <t>77334</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>95604</t>
+          <t>104530</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,6%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>180063</t>
+          <t>189171</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>172026</t>
+          <t>181187</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>186792</t>
+          <t>195743</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>214568</t>
+          <t>227531</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>204413</t>
+          <t>215582</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>223340</t>
+          <t>237480</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>394632</t>
+          <t>416702</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>382174</t>
+          <t>402853</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>407050</t>
+          <t>430049</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>84,76%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>204424</t>
+          <t>214436</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>204424</t>
+          <t>214436</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>204424</t>
+          <t>214436</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>273353</t>
+          <t>292947</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>273353</t>
+          <t>292947</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>273353</t>
+          <t>292947</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>477778</t>
+          <t>507383</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>477778</t>
+          <t>507383</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>477778</t>
+          <t>507383</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>85110</t>
+          <t>90364</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>71839</t>
+          <t>75881</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>99136</t>
+          <t>105557</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>188049</t>
+          <t>206583</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>100373</t>
+          <t>187084</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>241687</t>
+          <t>226763</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>273160</t>
+          <t>296947</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>172260</t>
+          <t>272374</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>320343</t>
+          <t>322447</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>20,01%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>563210</t>
+          <t>623868</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>549184</t>
+          <t>608675</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>576481</t>
+          <t>638351</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>839761</t>
+          <t>690552</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>786123</t>
+          <t>670372</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>927437</t>
+          <t>710051</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1402970</t>
+          <t>1314421</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1355787</t>
+          <t>1288921</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1503870</t>
+          <t>1338994</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>83,1%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>648320</t>
+          <t>714232</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>648320</t>
+          <t>714232</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>648320</t>
+          <t>714232</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1027810</t>
+          <t>897135</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1027810</t>
+          <t>897135</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1027810</t>
+          <t>897135</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1676130</t>
+          <t>1611368</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1676130</t>
+          <t>1611368</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1676130</t>
+          <t>1611368</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
